--- a/forms/trg/Formulir_TRG_pored-rg.xlsx
+++ b/forms/trg/Formulir_TRG_pored-rg.xlsx
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -937,16 +937,24 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Rachman Hakim, S.Pt., M.P</t>
+          <t>Dr. Ir. Wempie Pakiding, M.Sc</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -966,19 +974,15 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Daryatmo, S.Pt., M.P., IPM</t>
+          <t>Muhammad Rachman Hakim, S.Pt., M.P</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="n"/>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
@@ -999,24 +1003,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Adnan Ali Khalaf Alrubaye</t>
+          <t>Dr. Ir. Daryatmo, S.Pt., M.P., IPM</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>United State</t>
-        </is>
-      </c>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Andi Asnayanti</t>
+          <t>Dr. Adnan Ali Khalaf Alrubaye</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1073,16 +1073,24 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Muhammad Ihsan Andi Dagong, S.Pt., M.Si</t>
+          <t>Dr. Andi Asnayanti</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>United State</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1102,12 +1110,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Syahdar Baba, S.Pt., M.Si., IPU</t>
+          <t>Prof. Dr. Muhammad Ihsan Andi Dagong, S.Pt., M.Si</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1131,12 +1139,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>drh. Kusmandari Indah Prahesti, M.Si</t>
+          <t>Prof. Dr. Ir. Syahdar Baba, S.Pt., M.Si., IPU</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1160,12 +1168,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Febrina Angriani Majid</t>
+          <t>drh. Kusmandari Indah Prahesti, M.Si</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1189,12 +1197,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Misbah Ahmad Ruhani</t>
+          <t>Febrina Angriani Majid</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1218,20 +1226,16 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Yousif Altaher Edress Mohammed</t>
+          <t>Muhammad Misbah Ahmad Ruhani</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>Utilizing the advantages of local poultry, which exhibit a high degree of adaptation to local conditions, offers a significant opportunity for research in areas such as breeding, feed technology, disease resistance, and other traits, including meat and egg quality. This ultimately aims to produce local poultry breeds or lines of enhanced quality. Recognizing the importance of this matter motivates our team’s commitment to collecting a diverse range of local poultry genetics and developing them into a viable market commodity, all while retaining their core strengths.</t>
-        </is>
-      </c>
+      <c r="E14" s="11" t="n"/>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1249,10 +1253,22 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Yousif Altaher Edress Mohammed</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Utilizing the advantages of local poultry, which exhibit a high degree of adaptation to local conditions, offers a significant opportunity for research in areas such as breeding, feed technology, disease resistance, and other traits, including meat and egg quality. This ultimately aims to produce local poultry breeds or lines of enhanced quality. Recognizing the importance of this matter motivates our team’s commitment to collecting a diverse range of local poultry genetics and developing them into a viable market commodity, all while retaining their core strengths.</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1260,7 +1276,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1449,15 +1469,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
